--- a/www/download/COUNTRY.BRA.rpO2.xlsx
+++ b/www/download/COUNTRY.BRA.rpO2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Brasil</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.915734113517542</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>1.00469193759665</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>1.0775397229446</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>1.15970262026583</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>1.80401219237676</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>1.82715152306013</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>2.33426698569532</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>2.82845434464621</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>3.05819743146939</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>2.92039006162992</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>2.42365480933938</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>2.17533179323684</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>1.94704053129045</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>1.83376551466426</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>1.99942819729204</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>73.545</t>
+          <t>0.15816560308549</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>71.986</t>
+          <t>0.153446106891615</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>73.128</t>
+          <t>0.246316691298318</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>72.745</t>
+          <t>0.201629896070416</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>76.641</t>
+          <t>0.235304766246426</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>78.972</t>
+          <t>-0.170842464561194</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>79.544</t>
+          <t>-0.20170328709467</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>82.629</t>
+          <t>-0.0902334967151297</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>84.035</t>
+          <t>-0.108526951091816</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>88.252</t>
+          <t>-0.197138404569034</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>90.906</t>
+          <t>-0.254646365938885</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>93.247</t>
+          <t>-0.277221640057934</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>94.714</t>
+          <t>-0.217632886612892</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>96.233</t>
+          <t>-0.240066344156579</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>96.647</t>
+          <t>0.045951471768956</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>59.052</t>
+          <t>1.67702490054749</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>57.777</t>
+          <t>1.69085112580741</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>58.432</t>
+          <t>1.94137591512212</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>57.853</t>
+          <t>1.8535664290053</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>60.702</t>
+          <t>1.96313493708487</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>62.692</t>
+          <t>0.988513067624171</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>63.064</t>
+          <t>0.936400614811147</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>65.474</t>
+          <t>1.23299932919714</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>66.734</t>
+          <t>1.17877397817959</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>70.286</t>
+          <t>0.955280083014075</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>72.221</t>
+          <t>0.802948983791157</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>73.868</t>
+          <t>0.706535872632387</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>74.771</t>
+          <t>0.811295413834934</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>75.799</t>
+          <t>0.725265337388614</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>76.071</t>
+          <t>1.33481911900172</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>157522.872</t>
+          <t>3.10276419428286</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>154975.268</t>
+          <t>3.05984864656625</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>158449.89</t>
+          <t>3.37848316424403</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>158213.64</t>
+          <t>3.1699152309612</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>164642.11</t>
+          <t>3.24795155558527</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>170373.593</t>
+          <t>1.81423497524515</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>172038.194</t>
+          <t>1.70381717045332</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>179030.577</t>
+          <t>2.06633802582195</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>181564.871</t>
+          <t>1.93370302419645</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>189442.152</t>
+          <t>1.58129823284713</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>193103.106</t>
+          <t>1.3370471983447</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>197824.902</t>
+          <t>1.18385145893344</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>201071.541</t>
+          <t>1.28391412320938</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>204334.615</t>
+          <t>1.14105299474865</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>205284.27</t>
+          <t>1.84424456014149</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>124855.477</t>
+          <t>1115508531061.77</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>122981.929</t>
+          <t>1122538917510.14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>125000.246</t>
+          <t>1046882357283.05</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>124217.313</t>
+          <t>1036504080572.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>128568.971</t>
+          <t>1118164566993.52</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>133539.152</t>
+          <t>1554498363018.59</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>134738.042</t>
+          <t>1596324643370.1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>140161.944</t>
+          <t>1487259915998.09</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>142510.189</t>
+          <t>1533606775064.34</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>149104.054</t>
+          <t>1815324408341.98</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>151507.858</t>
+          <t>1913741950851.86</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>154756.786</t>
+          <t>2016052064822.94</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>156829.399</t>
+          <t>2096142194728.72</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>159080.283</t>
+          <t>2329442468646.74</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>159733.056</t>
+          <t>1640779761210.09</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>308461142342.603</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28.91</t>
+          <t>300186997276.44</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>278415090483.5</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>286836887303.641</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>288186413409.181</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>30.42</t>
+          <t>385011414678.925</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>396183098522.417</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>354516367889.615</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>342588642520.079</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>394906181891.423</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>434084808817.286</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>31.97</t>
+          <t>483209321447.791</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>505255297906.99</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>559374349690.16</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>33.34</t>
+          <t>434458925428.849</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>35769719.2152058</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>30.81</t>
+          <t>34149858.206346</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31.33</t>
+          <t>30435339.4774962</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31901075.7451843</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>47746925.3979546</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>55603633.2659498</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>33.42</t>
+          <t>66444459.4171784</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>65265555.3043075</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>58863904.7252599</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>35.61</t>
+          <t>56478603.0818665</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>45473678.8186553</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>40055851.3238119</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>33867627.5907663</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>30524637.9068749</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>24440603.8716024</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>170520.401771447</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>37.43</t>
+          <t>169417.751116076</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>36.53</t>
+          <t>166046.856294793</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>35.62</t>
+          <t>157558.13645252</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>34.72</t>
+          <t>147475.015478143</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>109057.706360917</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>32.92</t>
+          <t>99122.4578153937</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>32.01</t>
+          <t>105801.735575603</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>101913.537610853</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>114504.872789571</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>109807.10625851</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>119238.661308329</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>27.09</t>
+          <t>194154.525557112</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>26.04</t>
+          <t>226312.36768349</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>267596.325879229</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>467663.702988195</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>488677.629836954</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>448931.64894247</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>437189.110483749</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>439184.529838364</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>481543.29565864</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>470355.335969799</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>460494.763083101</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>485483.620634169</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>620729.228483145</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>632569.915853734</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>706222.387070263</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>935792.28413597</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>1163648.24798007</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>16.46</t>
+          <t>946617.365827791</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>1.51709157534113</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>1.48920667473864</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>1.68418675282418</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>30.88</t>
+          <t>1.55414124401596</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>1.5984998794691</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>0.746396583820014</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>0.673695153569632</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>35.57</t>
+          <t>0.894978485273946</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>37.02</t>
+          <t>0.834967031257527</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>0.636152643601029</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>39.92</t>
+          <t>0.495864385648551</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>0.399019786165701</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>0.466262284566219</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>43.26</t>
+          <t>0.38472343879412</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>44.38</t>
+          <t>0.857873870616867</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>176456.739795647</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>57.39</t>
+          <t>171881.591541854</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>171384.406107029</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>54.63</t>
+          <t>160891.712033725</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>53.26</t>
+          <t>113760.958790005</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>51.88</t>
+          <t>131607.250077569</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>118662.525337633</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>49.13</t>
+          <t>112217.792776431</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>47.34</t>
+          <t>120483.288061918</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>45.56</t>
+          <t>141621.64922617</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>179120.441546385</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>204740.203811757</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>40.04</t>
+          <t>252043.150529306</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>38.18</t>
+          <t>314590.733405019</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>36.31</t>
+          <t>296158.785803693</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.915734113517542</t>
+          <t>5223.56042504027</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.00469193759665</t>
+          <t>5195.61151790826</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.0775397229446</t>
+          <t>4764.78771110979</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.15970262026583</t>
+          <t>4958.00808904927</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.80401219237676</t>
+          <t>4747.5799306403</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.82715152306013</t>
+          <t>6141.34852140913</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.33426698569532</t>
+          <t>6282.19470853941</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.82845434464621</t>
+          <t>5414.60256821947</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3.05819743146939</t>
+          <t>5133.6704694058</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.92039006162992</t>
+          <t>5618.56424933327</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2.42365480933938</t>
+          <t>6010.46588159093</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2.17533179323684</t>
+          <t>6541.5135282547</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.94704053129045</t>
+          <t>6757.37362144509</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.83376551466426</t>
+          <t>7379.69275665525</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.99942819729204</t>
+          <t>5711.25067370941</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>259150807460.168</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>259155918192.649</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>230261924936.962</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>252968301786.686</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>289328136512.226</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>510980731672.542</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>548690720645.226</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>549997914678.06</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>595859414562.624</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>743454111300.378</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>880321541538.728</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>969897759956.498</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>866397569719.785</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>908189791815.948</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>533152016486.841</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>271927162967.768</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>272952878990.404</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>243322339671.948</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>266764072794.711</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>301052534453.535</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>539686444831.995</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>581595861220.609</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>567977678479.074</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>614241972923.093</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>754414720995.453</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>909370992517.021</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>999639540357.922</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>894518954251.167</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>941010181573.931</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>574963204858.83</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.658</t>
+          <t>-12776355507.6003</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.755</t>
+          <t>-13796960797.7549</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2.787</t>
+          <t>-13060414734.9858</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2.719</t>
+          <t>-13795771008.0258</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.895</t>
+          <t>-11724397941.3091</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.116</t>
+          <t>-28705713159.453</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.834</t>
+          <t>-32905140575.3826</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.768</t>
+          <t>-17979763801.0135</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.809</t>
+          <t>-18382558360.4698</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2.085</t>
+          <t>-10960609695.0753</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2.611</t>
+          <t>-29049450978.2929</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2.933</t>
+          <t>-29741780401.4231</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3.543</t>
+          <t>-28121384531.3819</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>4.244</t>
+          <t>-32820389757.9822</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>4.228</t>
+          <t>-41811188371.9882</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.262</t>
+          <t>13148.1799391542</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>12932.9508697262</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.421</t>
+          <t>12789.5800541803</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>12663.4529484055</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>12336.5858775387</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.097</t>
+          <t>10725.230077837</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>10514.4788374632</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>10260.555373085</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>9420.1160607</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>9192.82874978887</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.562</t>
+          <t>8990.84185342759</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.895</t>
+          <t>9151.70685749893</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.377</t>
+          <t>9908.08208384758</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.895</t>
+          <t>10218.8335312397</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.741</t>
+          <t>10610.7833952277</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>11601.1529575121</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>11325.6412858693</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>10975.8774600959</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.747</t>
+          <t>10732.7500733511</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>10376.0751110985</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>9155.98552568739</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.479</t>
+          <t>8914.87819991816</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>8712.57723925583</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>7970.25330189654</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>7763.18777743409</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>7608.27944281523</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.935</t>
+          <t>7772.8480974506</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>9711.37642159291</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.407</t>
+          <t>9831.38457461254</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>10096.3578283424</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15.82</t>
+          <t>55919.0744709033</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>15.34</t>
+          <t>55162.1956404715</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>24.63</t>
+          <t>59446.5520192967</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20.16</t>
+          <t>58540.8818546665</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>55558.9445026074</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-17.08</t>
+          <t>64412.2788355735</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-20.17</t>
+          <t>67952.387212892</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-9.02</t>
+          <t>73652.5956675123</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>83307.2466443061</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-19.71</t>
+          <t>109195.004740986</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-25.46</t>
+          <t>134029.798305241</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-27.72</t>
+          <t>156508.079884294</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-21.76</t>
+          <t>182673.133968401</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>225925.787330055</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>177168.145813593</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>167.7</t>
+          <t>74024665487.8765</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>169.09</t>
+          <t>70302764996.9558</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>194.14</t>
+          <t>66701603807.2698</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>185.36</t>
+          <t>71601437814.0429</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>196.31</t>
+          <t>101655345698.243</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>98.85</t>
+          <t>143538965953.777</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>93.64</t>
+          <t>179539101382.81</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>123.3</t>
+          <t>188741368801.247</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>117.88</t>
+          <t>195863896800.234</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>95.53</t>
+          <t>246474589367.784</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>80.29</t>
+          <t>250300118782.376</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>70.65</t>
+          <t>262616079889.362</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>81.13</t>
+          <t>252331595442.329</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>72.53</t>
+          <t>275511772408.712</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>133.48</t>
+          <t>161078883850.871</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>310.28</t>
+          <t>63624.5740749555</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>305.98</t>
+          <t>66099.9739901101</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>337.85</t>
+          <t>73317.6085475123</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>316.99</t>
+          <t>70462.4594564374</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>324.8</t>
+          <t>60009.8886529971</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>181.42</t>
+          <t>71432.036347915</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>170.38</t>
+          <t>71207.593913016</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>206.63</t>
+          <t>62298.8280490103</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>193.37</t>
+          <t>63637.2100849141</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>158.13</t>
+          <t>79039.9726229725</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>96807.0042247079</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>118.39</t>
+          <t>118387.998731804</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>128.39</t>
+          <t>153431.634813008</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>114.11</t>
+          <t>211376.023931242</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>184.42</t>
+          <t>168974.33912302</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>853209.365</t>
+          <t>365081036250.598</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>815283.598</t>
+          <t>372890200209.041</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>802646.558</t>
+          <t>344601454524.195</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>780752.41</t>
+          <t>369331278352.288</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>795232.859</t>
+          <t>412919147649.06</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>723069.666</t>
+          <t>703855302062.05</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>709128.762</t>
+          <t>752749770665.294</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>719912.128</t>
+          <t>656801795133.423</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>669780.085</t>
+          <t>655480864746.114</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>685120.52</t>
+          <t>798420088073.492</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>691635.763</t>
+          <t>882471295275.596</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>724794.479</t>
+          <t>996220703916.052</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>919802.423</t>
+          <t>983820512255.777</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>946099.788</t>
+          <t>1125034208294.27</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>975784.098</t>
+          <t>667667318343.127</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>776424.943</t>
+          <t>-7705.49960405221</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>747227.477</t>
+          <t>-10937.7783496386</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>747318.098</t>
+          <t>-13871.0565282157</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>732621.924</t>
+          <t>-11921.5776017709</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>748852.361</t>
+          <t>-4450.94415038973</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>672382.619</t>
+          <t>-7019.75751234143</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>663089.732</t>
+          <t>-3255.20670012402</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>671800.89</t>
+          <t>11353.7676185021</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>628638.864</t>
+          <t>19670.036559392</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>646126.793</t>
+          <t>30155.0321180136</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>649332.006</t>
+          <t>37222.794080533</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>676019.402</t>
+          <t>38120.0811524903</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>740836.787</t>
+          <t>29241.4991553926</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>774578.773</t>
+          <t>14549.7633988127</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>807169.885</t>
+          <t>8193.80669057303</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1115508.531</t>
+          <t>-291056370762.722</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1122538.918</t>
+          <t>-302587435212.085</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1046882.357</t>
+          <t>-277899850716.925</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1036504.081</t>
+          <t>-297729840538.245</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1118164.567</t>
+          <t>-311263801950.817</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1554498.363</t>
+          <t>-560316336108.273</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1596324.643</t>
+          <t>-573210669282.484</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1487259.916</t>
+          <t>-468060426332.176</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1533606.775</t>
+          <t>-459616967945.88</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1815324.408</t>
+          <t>-551945498705.708</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1913741.951</t>
+          <t>-632171176493.22</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2016052.065</t>
+          <t>-733604624026.691</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2096142.195</t>
+          <t>-731488916813.448</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2329442.469</t>
+          <t>-849522435885.563</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1640779.761</t>
+          <t>-506588434492.256</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>307826.44203</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.489</t>
+          <t>325696.19641</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>339814.34862</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>325817.53526</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>226786.80764</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>258213.76393</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>218486.14965</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>207952.31113</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>227846.57867</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.621</t>
+          <t>277971.10007</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>354224.1177</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>431003.88651</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.936</t>
+          <t>534472.07806</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.164</t>
+          <t>649810.03032</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.947</t>
+          <t>630373.14299</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>406738.778</t>
+          <t>0.052243997889939</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>389168.661</t>
+          <t>0.065799993055667</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>387211.56</t>
+          <t>0.0776988822262481</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>373544.646</t>
+          <t>0.0778435962654476</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>375471.643</t>
+          <t>0.0763542861746593</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>352055.625</t>
+          <t>0.0704698143911199</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>336408.689</t>
+          <t>0.0658454504105279</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>341707.861</t>
+          <t>0.0661604297998362</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>321937.312</t>
+          <t>0.0710038395042892</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>334869.829</t>
+          <t>0.0740190724686711</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>332204.331</t>
+          <t>0.0789540182471218</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>340390.44</t>
+          <t>0.087638324913398</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>434899.39</t>
+          <t>0.0643661972494932</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>453042.095</t>
+          <t>0.060265930537589</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>463826.94</t>
+          <t>0.0602964293712051</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>328022.217561222</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>357050.860492582</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>359800.07234588</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>354405.445036471</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>243070.117973706</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>261244.890042264</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>226361.85432922</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>208054.975411469</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>219695.42882029</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>261347.622060217</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>355201.572591124</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>445629.031897406</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>564910.169945729</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>691295.03710285</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>706701.547310895</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>308461.142</t>
+          <t>357464.215007532</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>300186.997</t>
+          <t>386261.837240327</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>278415.09</t>
+          <t>382909.754649366</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>286836.887</t>
+          <t>374196.607393886</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>288186.413</t>
+          <t>255838.859720888</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>385011.415</t>
+          <t>278432.354738735</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>396183.099</t>
+          <t>239810.05324894</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>354516.368</t>
+          <t>220899.745023004</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>342588.643</t>
+          <t>231929.903542001</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>394906.182</t>
+          <t>274582.276132272</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>434084.809</t>
+          <t>374878.242364804</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>483209.321</t>
+          <t>473406.172577666</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>505255.298</t>
+          <t>694954.107433865</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>559374.35</t>
+          <t>836641.718047541</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>434458.925</t>
+          <t>846505.046696694</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>151.71</t>
+          <t>2657544.91490704</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>148.92</t>
+          <t>2754537.28489732</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>168.42</t>
+          <t>2787196.46883731</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>155.41</t>
+          <t>2718929.34610389</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>159.85</t>
+          <t>1895367.49971133</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>2115917.71359179</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>67.37</t>
+          <t>1833706.71262236</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>1768386.41775049</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>1809238.63981075</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>63.62</t>
+          <t>2085356.56153879</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>2610569.13966916</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>2933384.85080145</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>46.63</t>
+          <t>3542955.74900728</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>4243999.76630099</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>85.79</t>
+          <t>4227866.28044271</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>357464.215007532</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>368611.060278216</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>30.435</t>
+          <t>367759.103557952</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>31.901</t>
+          <t>377762.247685968</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>47.747</t>
+          <t>371747.508532344</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>55.604</t>
+          <t>394993.174258897</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>66.444</t>
+          <t>395005.131467663</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>65.266</t>
+          <t>398454.12120389</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>58.864</t>
+          <t>399955.482576774</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>56.479</t>
+          <t>420381.380490107</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>45.474</t>
+          <t>441348.130864091</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>40.056</t>
+          <t>463664.07274651</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>33.868</t>
+          <t>570469.744645256</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>30.525</t>
+          <t>598485.341610338</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>24.441</t>
+          <t>596660.920536902</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>328022.217561222</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>339770.95492785</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>344721.618845927</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>357115.059466346</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>352424.195876436</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>371020.318605678</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>372873.535863077</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>375221.962253843</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>378721.31730579</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>400969.203275503</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>418931.130914099</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>437298.196131812</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>461894.667202679</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>492391.934259925</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>496391.703197306</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>315297.510722468</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>353130.125759673</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>387946.456280634</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>372542.950326114</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>258480.391269112</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>280715.578621265</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>239403.76975106</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>229214.998226996</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>248946.178067999</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>295977.807677728</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>385235.365035196</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>461817.138462334</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>480089.739116135</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>570359.328522459</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>551084.026373306</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>776424942710.667</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>747227477290.262</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>747318097662.155</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>732621924167.388</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>748852360508.389</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>672382619326.985</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>663089731923.17</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>671800889828.283</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>628638864307.615</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>646126793476.04</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>649332005860.839</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>676019401565.162</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>740836787398.288</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>774578773076.183</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>807169885410.541</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>853209365234.656</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>815283597544.761</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>802646557779.506</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>780752410486.841</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>795232858542.92</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>723069666061.562</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>709128762293.865</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>719912128445.145</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>669780084790.063</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>685120519721.932</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>691635763121.184</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>724794478947.597</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>919802422659.497</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>946099787697.319</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>975784098429.543</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>406738777631.694</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>389168661164.816</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>387211560483.25</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>373544645656.171</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>375471642603.556</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>352055625197.169</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>336408689391.983</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>341707860717.249</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>321937311801.82</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>334869828760.844</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>332204331065.831</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>340390440374.787</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>434899389765.288</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>453042095304.171</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>463826939507.778</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>73545221.6136996</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>71985645.4011104</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>73128236.0519808</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>72744860.8372439</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>76641008.2837895</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>78972347</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>79544414</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>82629067</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>84034981</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>88252473</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>90905673</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>93246963</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>94713909</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>96232609</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>96647139</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>59051895.1142841</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>57777028.9872046</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>58431793.2642276</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>57853251.1750386</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>60701750.7065571</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>62691673.2272644</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>63064441.1552358</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>65474125.4640584</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>66733664.4534825</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>70285959.9653567</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>72221491.2069989</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>73868122.3176669</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>74770957.8028244</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>75799138.0041801</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>76070715.5490115</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>157522871815.931</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>154975267826.828</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>158449890428.51</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>158213639601.25</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>164642110208.336</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>170373593179.634</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>172038193512.572</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>179030577348.644</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>181564871488.186</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>189442152116.396</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>193103105662.399</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>197824901761.945</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>201071540982.591</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>204334614712.513</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>205284270174.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>124855477356.272</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>122981929130.877</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>125000245608.597</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>124217313012.641</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>128568970516.355</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>133539151699.074</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>134738041576.624</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>140161944231.357</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>142510188701.274</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>149104053980.659</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>151507858121.156</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>154756786038.698</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>156829398560.943</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>159080283416.758</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>159733056266.715</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.28527207953238</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.289063672026907</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.292855264521435</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.296646857015962</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.30043844951049</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.304230042005017</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.308021634499545</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.311813226994072</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.312940804118395</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.314068381242717</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.31519595836704</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.319739582810603</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.324283207254166</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.32882683169773</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.333370456141293</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.302847446399263</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.308080715976869</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.313313985554475</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.318547255132081</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.323780524709687</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.329013794287293</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.334247063864899</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.339480333442505</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.347788509864734</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.356096686286962</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.36440486270919</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.370335501013448</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.376266139317706</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.382196777621964</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.388127415926222</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.383309045496929</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.374284183424795</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.365259321352662</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.356234459280528</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.347209597208395</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.338184735136261</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.329159873064128</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.320135010991994</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.310699257445443</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.301263503898892</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.291827750352342</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.28135348760452</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.270879224856699</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.260404962108878</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.249930699361057</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.110215680880114</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.112243117090419</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.114270553300723</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.116297989511028</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.118325425721333</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.120352861931638</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.122380298141942</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.124407734352247</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.127782000052277</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.131156265752308</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.134530531452338</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.142041661732327</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.149552792012316</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.157063922292304</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.164575052572293</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.273601964623949</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.285335237123337</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.297068509622725</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.308801782122114</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.320535054621502</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.33226832712089</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.344001599620279</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.355734872119667</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.370214731055326</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.384694589990986</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.399174448926646</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.41032044478257</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.421466440638494</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.432612436494418</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.443758432350343</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.587610925924509</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.573850217214816</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.560089508505123</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.54632879979543</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.532568091085737</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.518807382376044</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.50504667366635</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.491285964956657</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.473431840320967</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.455577715685277</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.437723591049587</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.419066464913674</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.400409338777762</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.381752212641849</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.363095086505936</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1261526.44119</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1366247.23366</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1420617.91803</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1380365.38991</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>969896.04007</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1096554.37795</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>948116.04885</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>897641.136</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>978595.75461</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1175437.15757</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1562385.44245</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1895074.57938</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2377320.84208</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2894929.56407</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2741154.20109</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>672761.72573</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>739391.963</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>770856.21093</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>746739.55772</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>514319.25099</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>559147.93336</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>479213.823</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>450114.74325</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>480876.08161</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>570560.08381</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>760113.6074</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>935223.31104</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1175043.84655</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1407001.04657</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1397589.07307</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2433604.55329256</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2496405.24300983</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2573259.57977903</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2650481.85683378</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2717570.77314825</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2799141.45096697</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2886846.91913392</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2963511.49594946</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>3029294.64737244</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>3121399.53784588</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>3243195.30579049</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>3429017.52373446</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>3675487.88361005</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>3959516.16837724</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>4181401.4404286</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
